--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-administration-radiopharmaceutique.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$117</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3647" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3679" uniqueCount="380">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1076,6 +1076,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturedMaterial.code.qualifier</t>
   </si>
   <si>
@@ -1109,6 +1113,22 @@
   </si>
   <si>
     <t>Material.lotNumberText</t>
+  </si>
+  <si>
+    <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturedMaterial.sdtcExpirationTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
+</t>
+  </si>
+  <si>
+    <t>The date and time the manufacturer no longer ensures the safety, quality, and/or proper functioning of the material.</t>
+  </si>
+  <si>
+    <t>There is a need in many situations that the materials used are of a specific quality or potency or functional status. The ending date for this guarantee is specified by the manufacturer. After that date, while the material may still provide the same characteristics, the manufacturer no longer takes responsibility that the product will perform as specified and denies responsibility for failure of the material after that date.</t>
+  </si>
+  <si>
+    <t>Material.sdtcExpirationTime</t>
   </si>
   <si>
     <t>SubstanceAdministration.consumable.manufacturedProduct.manufacturerOrganization</t>
@@ -1505,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK116"/>
+  <dimension ref="A1:AK117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="100.08203125" customWidth="true" bestFit="true"/>
@@ -1522,7 +1542,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -11781,7 +11801,7 @@
         <v>74</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>74</v>
+        <v>340</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>74</v>
@@ -11789,10 +11809,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11892,10 +11912,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -11923,7 +11943,7 @@
         <v>149</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>196</v>
@@ -11997,10 +12017,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12023,13 +12043,13 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12080,7 +12100,7 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12100,10 +12120,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12126,13 +12146,13 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12183,7 +12203,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12203,10 +12223,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12229,12 +12249,16 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
+      <c r="M106" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>74</v>
       </c>
@@ -12282,7 +12306,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -12302,10 +12326,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12328,7 +12352,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -12381,7 +12405,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -12401,10 +12425,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12415,7 +12439,7 @@
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>74</v>
@@ -12427,7 +12451,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12480,13 +12504,13 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>74</v>
@@ -12500,10 +12524,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12526,7 +12550,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -12579,7 +12603,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -12599,10 +12623,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12625,7 +12649,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -12678,7 +12702,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12698,10 +12722,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12724,7 +12748,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -12777,7 +12801,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -12797,10 +12821,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12823,7 +12847,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -12876,7 +12900,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -12896,10 +12920,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12922,7 +12946,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -12975,7 +12999,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -12995,10 +13019,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13021,7 +13045,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13074,7 +13098,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13094,10 +13118,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13120,7 +13144,7 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
@@ -13173,7 +13197,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13193,10 +13217,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13219,7 +13243,7 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
@@ -13272,7 +13296,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13290,8 +13314,107 @@
         <v>74</v>
       </c>
     </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L117" s="2"/>
+      <c r="M117" s="2"/>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK116">
+  <autoFilter ref="A1:AK117">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13301,7 +13424,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI115">
+  <conditionalFormatting sqref="A2:AI116">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
